--- a/wildlife/reports/United-Kingdom/composition/Abingdon/Flora/composition.xlsx
+++ b/wildlife/reports/United-Kingdom/composition/Abingdon/Flora/composition.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39">
@@ -863,17 +863,17 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>Winter Aconite</t>
+          <t>Cats Ear</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Cats Ear</t>
+          <t>Winter Aconite</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52">

--- a/wildlife/reports/United-Kingdom/composition/Abingdon/Flora/composition.xlsx
+++ b/wildlife/reports/United-Kingdom/composition/Abingdon/Flora/composition.xlsx
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39">
@@ -923,17 +923,17 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Greater Knapweed</t>
+          <t>Red Valerian</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>Red Valerian</t>
+          <t>Greater Knapweed</t>
         </is>
       </c>
       <c r="B51" t="n">

--- a/wildlife/reports/United-Kingdom/composition/Abingdon/Flora/composition.xlsx
+++ b/wildlife/reports/United-Kingdom/composition/Abingdon/Flora/composition.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39">
@@ -863,17 +863,17 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>Cats Ear</t>
+          <t>Winter Aconite</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Winter Aconite</t>
+          <t>Cats Ear</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -923,21 +923,21 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Red Valerian</t>
+          <t>Greater Knapweed</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>Greater Knapweed</t>
+          <t>Red Valerian</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52">

--- a/wildlife/reports/United-Kingdom/composition/Abingdon/Flora/composition.xlsx
+++ b/wildlife/reports/United-Kingdom/composition/Abingdon/Flora/composition.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33">
@@ -793,21 +793,21 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Pyramidal Orchid</t>
+          <t>Common Yarrow</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>Common Yarrow</t>
+          <t>Pyramidal Orchid</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39">
@@ -863,17 +863,17 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>Winter Aconite</t>
+          <t>Cats Ear</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Cats Ear</t>
+          <t>Winter Aconite</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -913,31 +913,31 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Shepherd's Purse</t>
+          <t>Red Valerian</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Greater Knapweed</t>
+          <t>Shepherd's Purse</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>Red Valerian</t>
+          <t>Greater Knapweed</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52">

--- a/wildlife/reports/United-Kingdom/composition/Abingdon/Flora/composition.xlsx
+++ b/wildlife/reports/United-Kingdom/composition/Abingdon/Flora/composition.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>White Campion</t>
+          <t>Common Cleavers</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -533,7 +533,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Common Cleavers</t>
+          <t>White Campion</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Horsetail</t>
+          <t>Cornflower</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -633,11 +633,11 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Cornflower</t>
+          <t>Horsetail</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25">
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38">
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45">
@@ -883,7 +883,7 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>Common Bird’s-Foot Trefoil</t>
+          <t>Ragged Robin</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -893,7 +893,7 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Ragged Robin</t>
+          <t>Red Valerian</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -903,17 +903,17 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Yellow Flag Iris</t>
+          <t>Common Bird’s-Foot Trefoil</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Red Valerian</t>
+          <t>Yellow Flag Iris</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -943,7 +943,7 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>Hemlock</t>
+          <t>Common Burdock</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -953,7 +953,7 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>Common Burdock</t>
+          <t>Lady’s Bedstraw</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -963,17 +963,17 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>Lady’s Bedstraw</t>
+          <t>Hemlock</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>Honeysuckle</t>
+          <t>Sweet Violet</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -983,7 +983,7 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>Sweet Violet</t>
+          <t>Common Field Speedwell</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -993,7 +993,7 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>Common Field Speedwell</t>
+          <t>Honeysuckle</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1013,7 +1013,7 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>Shining Crane's Bill</t>
+          <t>Creeping Thistle</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1023,7 +1023,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>Oxford Ragwort</t>
+          <t>Shining Crane's Bill</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1033,11 +1033,11 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>Creeping Thistle</t>
+          <t>Oxford Ragwort</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62">

--- a/wildlife/reports/United-Kingdom/composition/Abingdon/Flora/composition.xlsx
+++ b/wildlife/reports/United-Kingdom/composition/Abingdon/Flora/composition.xlsx
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26">
@@ -783,7 +783,7 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Snowdrop</t>
+          <t>Common Yarrow</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -793,11 +793,11 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Common Yarrow</t>
+          <t>Snowdrop</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38">
@@ -883,17 +883,17 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>Ragged Robin</t>
+          <t>Red Valerian</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Red Valerian</t>
+          <t>Ragged Robin</t>
         </is>
       </c>
       <c r="B47" t="n">
